--- a/03_kinesins_KDs/TableS7_kinesins_KDs.xlsx
+++ b/03_kinesins_KDs/TableS7_kinesins_KDs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nalytorres/Documents/GitHub/ERM1_TorresMangual/03_kinesins_KDs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EE1F1B-7485-C646-9857-7DF897EE3C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC74798-2CAD-A340-8527-2A1E58D7C60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5480" yWindow="680" windowWidth="24760" windowHeight="17400" xr2:uid="{2E47865C-5B6A-2C4D-BA8F-0F652FA7F24F}"/>
+    <workbookView xWindow="5480" yWindow="680" windowWidth="24760" windowHeight="17400" activeTab="3" xr2:uid="{2E47865C-5B6A-2C4D-BA8F-0F652FA7F24F}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="4" r:id="rId1"/>
@@ -43,7 +43,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="315">
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>sd</t>
+  </si>
   <si>
     <t>Description</t>
   </si>
@@ -124,13 +130,892 @@
   </si>
   <si>
     <t>sd_total_molecules</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>contrast</t>
+  </si>
+  <si>
+    <t>null.value</t>
+  </si>
+  <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>conf.low</t>
+  </si>
+  <si>
+    <t>conf.high</t>
+  </si>
+  <si>
+    <t>adj.p.value</t>
+  </si>
+  <si>
+    <t>KLP-9-L4440</t>
+  </si>
+  <si>
+    <t>BMK-1-L4440</t>
+  </si>
+  <si>
+    <t>KLP-19-L4440</t>
+  </si>
+  <si>
+    <t>UNC-116-L4440</t>
+  </si>
+  <si>
+    <t>BMK-1-KLP-9</t>
+  </si>
+  <si>
+    <t>KLP-19-KLP-9</t>
+  </si>
+  <si>
+    <t>UNC-116-KLP-9</t>
+  </si>
+  <si>
+    <t>KLP-19-BMK-1</t>
+  </si>
+  <si>
+    <t>UNC-116-BMK-1</t>
+  </si>
+  <si>
+    <t>UNC-116-KLP-19</t>
+  </si>
+  <si>
+    <t>&lt;fctr&gt;</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>set3_mRNA</t>
+  </si>
+  <si>
+    <t>L4440</t>
+  </si>
+  <si>
+    <t>KLP-9</t>
+  </si>
+  <si>
+    <t>BMK-1</t>
+  </si>
+  <si>
+    <t>KLP-19</t>
+  </si>
+  <si>
+    <t>UNC-116</t>
+  </si>
+  <si>
+    <t>erm1_mRNA</t>
+  </si>
+  <si>
+    <t>The value under the null hypothesis (0 = no difference in means between the two groups).</t>
+  </si>
+  <si>
+    <t>The estimated difference in group means (GroupA mean − GroupB mean), in units of total mRNA molecules.</t>
+  </si>
+  <si>
+    <t>Lower bound of the 95% family-wise confidence interval for the estimated difference.</t>
+  </si>
+  <si>
+    <t>Upper bound of the 95% family-wise confidence interval for the estimated difference.</t>
+  </si>
+  <si>
+    <t>Tukey HSD-adjusted p-value for the comparison, corrected for multiple testing across all pairwise contrasts. A value &lt; 0.05 indicates a statistically significant difference between the two groups.</t>
+  </si>
+  <si>
+    <t>The subdirectory used as the grouping variable (RNAi condition).</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pairwise comparison being made, formatted as </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>GroupA-GroupB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_02.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_03.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_04.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_05.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_06.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_07.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_08.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_09.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_10.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_11.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_12</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_12.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_13</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_13.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_14</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_14.csv</t>
+  </si>
+  <si>
+    <t>230408_BMk-1_RNAi_LP306_15</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230408_BMk-1_RNAi_LP306_15.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_01.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_03.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_05.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_06.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_09.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_10.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_11.csv</t>
+  </si>
+  <si>
+    <t>231107_LP306_BMK-1_13</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231107_LP306_BMK-1_13.csv</t>
+  </si>
+  <si>
+    <t>231113_LP306_BMK-1_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231113_LP306_BMK-1_01.csv</t>
+  </si>
+  <si>
+    <t>231113_LP306_BMK-1_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231113_LP306_BMK-1_02.csv</t>
+  </si>
+  <si>
+    <t>231113_LP306_BMK-1_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231113_LP306_BMK-1_03.csv</t>
+  </si>
+  <si>
+    <t>231113_LP306_BMK-1_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231113_LP306_BMK-1_04.csv</t>
+  </si>
+  <si>
+    <t>231113_LP306_BMK-1_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231113_LP306_BMK-1_05.csv</t>
+  </si>
+  <si>
+    <t>231113_LP306_BMK-1_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231113_LP306_BMK-1_06.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_02.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_03.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_06.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_07.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_08.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_09.csv</t>
+  </si>
+  <si>
+    <t>231228_LP306_KLP-19_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231228_LP306_KLP-19_10.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_01.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_02.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_03.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_05.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_06.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_07.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_08.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_10.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_11.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_12</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_12.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_13</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_13.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_KLP-19_14</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_KLP-19_14.csv</t>
+  </si>
+  <si>
+    <t>240123_KLP-19_RNAi_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_KLP-19_RNAi_01.csv</t>
+  </si>
+  <si>
+    <t>240123_KLP-19_RNAi_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_KLP-19_RNAi_02.csv</t>
+  </si>
+  <si>
+    <t>240123_KLP-19_RNAi_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_KLP-19_RNAi_04.csv</t>
+  </si>
+  <si>
+    <t>240123_KLP-19_RNAi_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_KLP-19_RNAi_05.csv</t>
+  </si>
+  <si>
+    <t>240123_KLP-19_RNAi_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_KLP-19_RNAi_07.csv</t>
+  </si>
+  <si>
+    <t>240123_KLP-19_RNAi_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_KLP-19_RNAi_08.csv</t>
+  </si>
+  <si>
+    <t>231109_LP306_KLP-9_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231109_LP306_KLP-9_02.csv</t>
+  </si>
+  <si>
+    <t>231109_LP306_KLP-9_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231109_LP306_KLP-9_03.csv</t>
+  </si>
+  <si>
+    <t>231109_LP306_KLP-9_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231109_LP306_KLP-9_06.csv</t>
+  </si>
+  <si>
+    <t>231208_LP306_KLP-9_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231208_LP306_KLP-9_01.csv</t>
+  </si>
+  <si>
+    <t>231208_LP306_KLP-9_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231208_LP306_KLP-9_04.csv</t>
+  </si>
+  <si>
+    <t>231208_LP306_KLP-9_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231208_LP306_KLP-9_05.csv</t>
+  </si>
+  <si>
+    <t>231208_LP306_KLP-9_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231208_LP306_KLP-9_07.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_01.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_03.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_04.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_05.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_07.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_08.csv</t>
+  </si>
+  <si>
+    <t>231224_LP306_klp-9_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_231224_LP306_klp-9_11.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_01.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_02.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_03.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_04.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_05.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_06.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_07.csv</t>
+  </si>
+  <si>
+    <t>230828_L4440_RNAi_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_230828_L4440_RNAi_08.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_01.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_02.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_03.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_04.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_05.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_06.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_07.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_09.csv</t>
+  </si>
+  <si>
+    <t>240122_LP306_L4440_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240122_LP306_L4440_10.csv</t>
+  </si>
+  <si>
+    <t>240131_L4440_RNAi_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240131_L4440_RNAi_01.csv</t>
+  </si>
+  <si>
+    <t>240131_L4440_RNAi_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240131_L4440_RNAi_02.csv</t>
+  </si>
+  <si>
+    <t>240131_L4440_RNAi_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240131_L4440_RNAi_03.csv</t>
+  </si>
+  <si>
+    <t>240131_L4440_RNAi_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240131_L4440_RNAi_04.csv</t>
+  </si>
+  <si>
+    <t>240131_L4440_RNAi_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240131_L4440_RNAi_05.csv</t>
+  </si>
+  <si>
+    <t>240131_L4440_RNAi_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240131_L4440_RNAi_09.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_01.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_02.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_03.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_04.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_06.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_08.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_10.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_11.csv</t>
+  </si>
+  <si>
+    <t>240106_LP306_UNC-116_RNAi_12</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240106_LP306_UNC-116_RNAi_12.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_01.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_02.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_06.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_07.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_08.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_09.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_10.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_11.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_13</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_13.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_15</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_15.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_16</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_16.csv</t>
+  </si>
+  <si>
+    <t>240120_LP306_UNC-116_17</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240120_LP306_UNC-116_17.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_01</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_01.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_02</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_02.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_03</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_03.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_04</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_04.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_05</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_05.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_06</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_06.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_07</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_07.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_08</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_08.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_09</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_09.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_10</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_10.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_11</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_11.csv</t>
+  </si>
+  <si>
+    <t>240123_unc116_RNAi_12</t>
+  </si>
+  <si>
+    <t>total_mRNA_counts_240123_unc116_RNAi_12.csv</t>
+  </si>
+  <si>
+    <t>unique identifier of image: date_misc_strain_treatment_imageNumber</t>
+  </si>
+  <si>
+    <t>total number of spots per embryo - as reported with WormLib</t>
+  </si>
+  <si>
+    <t>longer image ID. Redundant with above</t>
+  </si>
+  <si>
+    <t>treatment condition</t>
+  </si>
+  <si>
+    <t>mRNA species observed by smFISH</t>
+  </si>
+  <si>
+    <t>mean total number of mRNA molecules per embryo averaged across all embryos</t>
+  </si>
+  <si>
+    <t>standard deviation of the mean above</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -217,6 +1102,76 @@
       <name val="Lucida Sans"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -238,7 +1193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -267,13 +1222,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -608,254 +1573,742 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF4FD9A-8CC9-294A-86D4-1970C3AC1875}">
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U68"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="27">
       <c r="A1" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="25">
       <c r="A2" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="20">
       <c r="A4" s="3" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="4"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="20">
       <c r="A10" s="9" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="6"/>
       <c r="B11" s="14" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="5"/>
       <c r="B12" s="13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="20">
       <c r="A15" s="10" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" s="13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="15" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="15"/>
-      <c r="C18" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C18" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="15" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B19" s="15"/>
-      <c r="C19" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C19" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21" s="15"/>
       <c r="C21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="15"/>
       <c r="B22" s="15"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" s="15"/>
       <c r="B23" s="15"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" s="15"/>
       <c r="B24" s="15"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="26" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="17"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="20">
+      <c r="A26" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="16"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="13" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B27" s="13"/>
       <c r="C27" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B28" s="12"/>
       <c r="C28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+        <v>24</v>
+      </c>
+      <c r="D28" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+        <v>24</v>
+      </c>
+      <c r="D29" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="20">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="12"/>
     </row>
-    <row r="34" spans="1:2" ht="20" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+    <row r="34" spans="1:21" ht="21">
+      <c r="A34" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="16"/>
-    </row>
-    <row r="42" spans="1:2" ht="20" x14ac:dyDescent="0.25"/>
+      <c r="C35" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E35" s="20"/>
+    </row>
+    <row r="36" spans="1:21" ht="17">
+      <c r="A36" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="28"/>
+    </row>
+    <row r="37" spans="1:21" ht="17">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="28"/>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>27</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="28"/>
+    </row>
+    <row r="39" spans="1:21" ht="21">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" t="s">
+        <v>27</v>
+      </c>
+      <c r="D39" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="28"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="20"/>
+      <c r="N39" s="20"/>
+      <c r="O39" s="20"/>
+      <c r="P39" s="20"/>
+      <c r="Q39" s="20"/>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>33</v>
+      </c>
+      <c r="C40" t="s">
+        <v>27</v>
+      </c>
+      <c r="D40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="28"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="19"/>
+      <c r="M40" s="20"/>
+      <c r="N40" s="20"/>
+      <c r="O40" s="20"/>
+      <c r="P40" s="20"/>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="28"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="19"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+    </row>
+    <row r="42" spans="1:21" ht="20" customHeight="1">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s">
+        <v>59</v>
+      </c>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21"/>
+      <c r="M42" s="21"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
+      <c r="P42" s="20"/>
+      <c r="Q42" s="20"/>
+      <c r="R42" s="20"/>
+      <c r="S42" s="20"/>
+      <c r="T42" s="20"/>
+      <c r="U42" s="20"/>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="20"/>
+      <c r="P43" s="20"/>
+      <c r="Q43" s="20"/>
+      <c r="R43" s="20"/>
+      <c r="S43" s="20"/>
+      <c r="T43" s="20"/>
+      <c r="U43" s="20"/>
+    </row>
+    <row r="44" spans="1:21" ht="21">
+      <c r="K44" s="18"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="20"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="20"/>
+      <c r="P44" s="20"/>
+      <c r="Q44" s="20"/>
+      <c r="R44" s="20"/>
+      <c r="S44" s="20"/>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="8"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="20"/>
+      <c r="P45" s="20"/>
+      <c r="Q45" s="20"/>
+      <c r="R45" s="20"/>
+      <c r="S45" s="20"/>
+      <c r="T45" s="20"/>
+      <c r="U45" s="20"/>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="20"/>
+      <c r="P46" s="20"/>
+      <c r="Q46" s="20"/>
+      <c r="R46" s="20"/>
+      <c r="S46" s="20"/>
+      <c r="T46" s="20"/>
+      <c r="U46" s="20"/>
+    </row>
+    <row r="47" spans="1:21">
+      <c r="K47" s="20"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="20"/>
+      <c r="O47" s="20"/>
+      <c r="P47" s="20"/>
+      <c r="Q47" s="20"/>
+      <c r="R47" s="20"/>
+      <c r="S47" s="20"/>
+      <c r="T47" s="20"/>
+    </row>
+    <row r="48" spans="1:21">
+      <c r="K48" s="20"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+    </row>
+    <row r="49" spans="11:21">
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="20"/>
+      <c r="P49" s="20"/>
+      <c r="Q49" s="20"/>
+      <c r="R49" s="20"/>
+      <c r="S49" s="20"/>
+      <c r="T49" s="20"/>
+      <c r="U49" s="20"/>
+    </row>
+    <row r="50" spans="11:21">
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="20"/>
+      <c r="R50" s="20"/>
+      <c r="S50" s="20"/>
+      <c r="T50" s="20"/>
+      <c r="U50" s="20"/>
+    </row>
+    <row r="51" spans="11:21">
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+      <c r="S51" s="20"/>
+      <c r="T51" s="20"/>
+      <c r="U51" s="20"/>
+    </row>
+    <row r="52" spans="11:21">
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+    </row>
+    <row r="53" spans="11:21" ht="21">
+      <c r="K53" s="18"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="20"/>
+      <c r="N53" s="20"/>
+      <c r="O53" s="20"/>
+      <c r="P53" s="20"/>
+      <c r="Q53" s="20"/>
+      <c r="R53" s="20"/>
+      <c r="S53" s="20"/>
+      <c r="T53" s="20"/>
+    </row>
+    <row r="54" spans="11:21">
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+      <c r="T54" s="20"/>
+      <c r="U54" s="20"/>
+    </row>
+    <row r="55" spans="11:21">
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="20"/>
+      <c r="N55" s="20"/>
+      <c r="O55" s="20"/>
+      <c r="P55" s="20"/>
+      <c r="Q55" s="20"/>
+      <c r="R55" s="20"/>
+      <c r="S55" s="20"/>
+      <c r="T55" s="20"/>
+      <c r="U55" s="20"/>
+    </row>
+    <row r="56" spans="11:21">
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="20"/>
+      <c r="N56" s="20"/>
+      <c r="O56" s="20"/>
+      <c r="P56" s="20"/>
+      <c r="Q56" s="20"/>
+      <c r="R56" s="20"/>
+      <c r="S56" s="20"/>
+      <c r="T56" s="20"/>
+      <c r="U56" s="20"/>
+    </row>
+    <row r="57" spans="11:21">
+      <c r="K57" s="20"/>
+      <c r="L57" s="20"/>
+      <c r="M57" s="20"/>
+      <c r="N57" s="20"/>
+      <c r="O57" s="20"/>
+      <c r="P57" s="20"/>
+      <c r="Q57" s="20"/>
+      <c r="R57" s="20"/>
+      <c r="S57" s="20"/>
+      <c r="T57" s="20"/>
+    </row>
+    <row r="58" spans="11:21">
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="20"/>
+      <c r="N58" s="20"/>
+      <c r="O58" s="20"/>
+      <c r="P58" s="20"/>
+      <c r="Q58" s="20"/>
+      <c r="R58" s="20"/>
+      <c r="S58" s="20"/>
+      <c r="T58" s="20"/>
+    </row>
+    <row r="59" spans="11:21">
+      <c r="K59" s="20"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="20"/>
+      <c r="N59" s="20"/>
+      <c r="O59" s="20"/>
+      <c r="P59" s="20"/>
+      <c r="Q59" s="20"/>
+      <c r="R59" s="20"/>
+      <c r="S59" s="20"/>
+      <c r="T59" s="20"/>
+      <c r="U59" s="20"/>
+    </row>
+    <row r="60" spans="11:21">
+      <c r="K60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="20"/>
+      <c r="N60" s="20"/>
+      <c r="O60" s="20"/>
+      <c r="P60" s="20"/>
+      <c r="Q60" s="20"/>
+      <c r="R60" s="20"/>
+      <c r="S60" s="20"/>
+      <c r="T60" s="20"/>
+      <c r="U60" s="20"/>
+    </row>
+    <row r="61" spans="11:21" ht="21">
+      <c r="K61" s="18"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="20"/>
+      <c r="N61" s="20"/>
+      <c r="O61" s="20"/>
+      <c r="P61" s="20"/>
+      <c r="Q61" s="20"/>
+      <c r="R61" s="20"/>
+      <c r="S61" s="20"/>
+      <c r="T61" s="20"/>
+    </row>
+    <row r="62" spans="11:21">
+      <c r="K62" s="8"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="8"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="20"/>
+      <c r="U62" s="20"/>
+    </row>
+    <row r="63" spans="11:21">
+      <c r="K63" s="23"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="20"/>
+      <c r="R63" s="20"/>
+      <c r="S63" s="20"/>
+      <c r="T63" s="20"/>
+      <c r="U63" s="20"/>
+    </row>
+    <row r="64" spans="11:21">
+      <c r="K64" s="23"/>
+      <c r="L64" s="20"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="20"/>
+      <c r="R64" s="20"/>
+      <c r="S64" s="20"/>
+      <c r="T64" s="20"/>
+      <c r="U64" s="20"/>
+    </row>
+    <row r="65" spans="11:21">
+      <c r="K65" s="23"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+      <c r="S65" s="20"/>
+      <c r="T65" s="20"/>
+      <c r="U65" s="20"/>
+    </row>
+    <row r="66" spans="11:21">
+      <c r="K66" s="23"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+      <c r="S66" s="20"/>
+      <c r="T66" s="20"/>
+      <c r="U66" s="20"/>
+    </row>
+    <row r="67" spans="11:21">
+      <c r="K67" s="23"/>
+      <c r="L67" s="20"/>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="20"/>
+      <c r="R67" s="20"/>
+      <c r="S67" s="20"/>
+      <c r="T67" s="20"/>
+    </row>
+    <row r="68" spans="11:21">
+      <c r="K68" s="20"/>
+      <c r="L68" s="20"/>
+      <c r="M68" s="20"/>
+      <c r="N68" s="20"/>
+      <c r="O68" s="20"/>
+      <c r="P68" s="20"/>
+      <c r="Q68" s="20"/>
+      <c r="R68" s="20"/>
+      <c r="S68" s="20"/>
+      <c r="T68" s="20"/>
+      <c r="U68" s="20"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A34:B34"/>
+  <mergeCells count="14">
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="A24:B24"/>
@@ -877,27 +2330,2599 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46F1505-F7F2-7349-822C-7CE1A7E41879}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:E124"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="31.1640625" customWidth="1"/>
+    <col min="4" max="4" width="48.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="25">
+        <v>568</v>
+      </c>
+      <c r="C2" s="25">
+        <v>2488</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="25">
+        <v>459</v>
+      </c>
+      <c r="C3" s="25">
+        <v>1384</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="25">
+        <v>632</v>
+      </c>
+      <c r="C4" s="25">
+        <v>2398</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="25">
+        <v>1284</v>
+      </c>
+      <c r="C5" s="25">
+        <v>4000</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="25">
+        <v>854</v>
+      </c>
+      <c r="C6" s="25">
+        <v>3350</v>
+      </c>
+      <c r="D6" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="25">
+        <v>1416</v>
+      </c>
+      <c r="C7" s="25">
+        <v>4487</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" s="25">
+        <v>1359</v>
+      </c>
+      <c r="C8" s="25">
+        <v>3719</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="25">
+        <v>1338</v>
+      </c>
+      <c r="C9" s="25">
+        <v>3225</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="25">
+        <v>715</v>
+      </c>
+      <c r="C10" s="25">
+        <v>2504</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="25">
+        <v>1216</v>
+      </c>
+      <c r="C11" s="25">
+        <v>3396</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="25">
+        <v>1218</v>
+      </c>
+      <c r="C12" s="25">
+        <v>2871</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="25">
+        <v>1073</v>
+      </c>
+      <c r="C13" s="25">
+        <v>3309</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="25">
+        <v>808</v>
+      </c>
+      <c r="C14" s="25">
+        <v>1627</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="25">
+        <v>1000</v>
+      </c>
+      <c r="C15" s="25">
+        <v>2933</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="25">
+        <v>497</v>
+      </c>
+      <c r="C16" s="25">
+        <v>4018</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="25">
+        <v>718</v>
+      </c>
+      <c r="C17" s="25">
+        <v>3711</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="25">
+        <v>1109</v>
+      </c>
+      <c r="C18" s="25">
+        <v>3045</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="25">
+        <v>1296</v>
+      </c>
+      <c r="C19" s="25">
+        <v>2824</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="B20" s="25">
+        <v>1328</v>
+      </c>
+      <c r="C20" s="25">
+        <v>3056</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="25">
+        <v>1329</v>
+      </c>
+      <c r="C21" s="25">
+        <v>3318</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" s="25">
+        <v>1318</v>
+      </c>
+      <c r="C22" s="25">
+        <v>3551</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" s="25">
+        <v>1287</v>
+      </c>
+      <c r="C23" s="25">
+        <v>3680</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="25">
+        <v>2002</v>
+      </c>
+      <c r="C24" s="25">
+        <v>3451</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="25">
+        <v>788</v>
+      </c>
+      <c r="C25" s="25">
+        <v>3442</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="25">
+        <v>765</v>
+      </c>
+      <c r="C26" s="25">
+        <v>2816</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="25">
+        <v>687</v>
+      </c>
+      <c r="C27" s="25">
+        <v>4402</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="25">
+        <v>916</v>
+      </c>
+      <c r="C28" s="25">
+        <v>4108</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="E28" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B29" s="25">
+        <v>1168</v>
+      </c>
+      <c r="C29" s="25">
+        <v>4358</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="B30" s="25">
+        <v>825</v>
+      </c>
+      <c r="C30" s="25">
+        <v>3338</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="25">
+        <v>1043</v>
+      </c>
+      <c r="C31" s="25">
+        <v>2360</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="25">
+        <v>1862</v>
+      </c>
+      <c r="C32" s="25">
+        <v>4916</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="B33" s="25">
+        <v>1630</v>
+      </c>
+      <c r="C33" s="25">
+        <v>2958</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="25">
+        <v>1602</v>
+      </c>
+      <c r="C34" s="25">
+        <v>3603</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B35" s="25">
+        <v>1563</v>
+      </c>
+      <c r="C35" s="25">
+        <v>3803</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="25">
+        <v>1215</v>
+      </c>
+      <c r="C36" s="25">
+        <v>2069</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="25">
+        <v>3262</v>
+      </c>
+      <c r="C37" s="25">
+        <v>3058</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="B38" s="25">
+        <v>1277</v>
+      </c>
+      <c r="C38" s="25">
+        <v>3760</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" s="25">
+        <v>3053</v>
+      </c>
+      <c r="C39" s="25">
+        <v>2949</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="25">
+        <v>542</v>
+      </c>
+      <c r="C40" s="25">
+        <v>3175</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B41" s="25">
+        <v>1015</v>
+      </c>
+      <c r="C41" s="25">
+        <v>3721</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B42" s="25">
+        <v>1313</v>
+      </c>
+      <c r="C42" s="25">
+        <v>4032</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="B43" s="25">
+        <v>996</v>
+      </c>
+      <c r="C43" s="25">
+        <v>3882</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" s="25">
+        <v>1097</v>
+      </c>
+      <c r="C44" s="25">
+        <v>4055</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" s="25">
+        <v>1017</v>
+      </c>
+      <c r="C45" s="25">
+        <v>3955</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="B46" s="25">
+        <v>1129</v>
+      </c>
+      <c r="C46" s="25">
+        <v>4052</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="25">
+        <v>1300</v>
+      </c>
+      <c r="C47" s="25">
+        <v>3812</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="24" t="s">
+        <v>154</v>
+      </c>
+      <c r="B48" s="25">
+        <v>984</v>
+      </c>
+      <c r="C48" s="25">
+        <v>3258</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="B49" s="25">
+        <v>1894</v>
+      </c>
+      <c r="C49" s="25">
+        <v>3750</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B50" s="25">
+        <v>4006</v>
+      </c>
+      <c r="C50" s="25">
+        <v>3625</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="B51" s="25">
+        <v>1104</v>
+      </c>
+      <c r="C51" s="25">
+        <v>4328</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="E51" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B52" s="25">
+        <v>1275</v>
+      </c>
+      <c r="C52" s="25">
+        <v>4309</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B53" s="25">
+        <v>610</v>
+      </c>
+      <c r="C53" s="25">
+        <v>3038</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B54" s="25">
+        <v>1051</v>
+      </c>
+      <c r="C54" s="25">
+        <v>4192</v>
+      </c>
+      <c r="D54" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="25">
+        <v>690</v>
+      </c>
+      <c r="C55" s="25">
+        <v>2769</v>
+      </c>
+      <c r="D55" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B56" s="25">
+        <v>518</v>
+      </c>
+      <c r="C56" s="25">
+        <v>2074</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="B57" s="25">
+        <v>471</v>
+      </c>
+      <c r="C57" s="25">
+        <v>2814</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" s="25">
+        <v>1775</v>
+      </c>
+      <c r="C58" s="25">
+        <v>3369</v>
+      </c>
+      <c r="D58" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="E58" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B59" s="25">
+        <v>1229</v>
+      </c>
+      <c r="C59" s="25">
+        <v>4184</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="B60" s="25">
+        <v>1197</v>
+      </c>
+      <c r="C60" s="25">
+        <v>4721</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61" s="25">
+        <v>882</v>
+      </c>
+      <c r="C61" s="25">
+        <v>2808</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>181</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="25">
+        <v>1156</v>
+      </c>
+      <c r="C62" s="25">
+        <v>3527</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="E62" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B63" s="25">
+        <v>1667</v>
+      </c>
+      <c r="C63" s="25">
+        <v>2827</v>
+      </c>
+      <c r="D63" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B64" s="25">
+        <v>1039</v>
+      </c>
+      <c r="C64" s="25">
+        <v>2501</v>
+      </c>
+      <c r="D64" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="E64" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B65" s="25">
+        <v>1106</v>
+      </c>
+      <c r="C65" s="25">
+        <v>2723</v>
+      </c>
+      <c r="D65" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B66" s="25">
+        <v>1008</v>
+      </c>
+      <c r="C66" s="25">
+        <v>2172</v>
+      </c>
+      <c r="D66" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="E66" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="B67" s="25">
+        <v>1901</v>
+      </c>
+      <c r="C67" s="25">
+        <v>3802</v>
+      </c>
+      <c r="D67" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B68" s="25">
+        <v>674</v>
+      </c>
+      <c r="C68" s="25">
+        <v>1999</v>
+      </c>
+      <c r="D68" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E68" s="25" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="B69" s="25">
+        <v>2927</v>
+      </c>
+      <c r="C69" s="25">
+        <v>4005</v>
+      </c>
+      <c r="D69" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="B70" s="25">
+        <v>1449</v>
+      </c>
+      <c r="C70" s="25">
+        <v>3550</v>
+      </c>
+      <c r="D70" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B71" s="25">
+        <v>363</v>
+      </c>
+      <c r="C71" s="25">
+        <v>3232</v>
+      </c>
+      <c r="D71" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="E71" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="B72" s="25">
+        <v>1074</v>
+      </c>
+      <c r="C72" s="25">
+        <v>3063</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B73" s="25">
+        <v>1067</v>
+      </c>
+      <c r="C73" s="25">
+        <v>3121</v>
+      </c>
+      <c r="D73" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="B74" s="25">
+        <v>1156</v>
+      </c>
+      <c r="C74" s="25">
+        <v>3287</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="B75" s="25">
+        <v>742</v>
+      </c>
+      <c r="C75" s="25">
+        <v>2125</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B76" s="25">
+        <v>1216</v>
+      </c>
+      <c r="C76" s="25">
+        <v>3172</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="B77" s="25">
+        <v>1208</v>
+      </c>
+      <c r="C77" s="25">
+        <v>3602</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="E77" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="B78" s="25">
+        <v>1180</v>
+      </c>
+      <c r="C78" s="25">
+        <v>3812</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="E78" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="B79" s="25">
+        <v>1039</v>
+      </c>
+      <c r="C79" s="25">
+        <v>3078</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="E79" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B80" s="25">
+        <v>1267</v>
+      </c>
+      <c r="C80" s="25">
+        <v>3807</v>
+      </c>
+      <c r="D80" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="E80" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="B81" s="25">
+        <v>979</v>
+      </c>
+      <c r="C81" s="25">
+        <v>3556</v>
+      </c>
+      <c r="D81" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="E81" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="B82" s="25">
+        <v>1284</v>
+      </c>
+      <c r="C82" s="25">
+        <v>4561</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E82" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="B83" s="25">
+        <v>936</v>
+      </c>
+      <c r="C83" s="25">
+        <v>3665</v>
+      </c>
+      <c r="D83" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="E83" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B84" s="25">
+        <v>1296</v>
+      </c>
+      <c r="C84" s="25">
+        <v>3674</v>
+      </c>
+      <c r="D84" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E84" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B85" s="25">
+        <v>1239</v>
+      </c>
+      <c r="C85" s="25">
+        <v>3563</v>
+      </c>
+      <c r="D85" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="E85" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="B86" s="25">
+        <v>771</v>
+      </c>
+      <c r="C86" s="25">
+        <v>2708</v>
+      </c>
+      <c r="D86" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="E86" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B87" s="25">
+        <v>591</v>
+      </c>
+      <c r="C87" s="25">
+        <v>2742</v>
+      </c>
+      <c r="D87" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="E87" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B88" s="25">
+        <v>930</v>
+      </c>
+      <c r="C88" s="25">
+        <v>3615</v>
+      </c>
+      <c r="D88" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E88" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B89" s="25">
+        <v>201</v>
+      </c>
+      <c r="C89" s="25">
+        <v>1421</v>
+      </c>
+      <c r="D89" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E89" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B90" s="25">
+        <v>709</v>
+      </c>
+      <c r="C90" s="25">
+        <v>3269</v>
+      </c>
+      <c r="D90" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="E90" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B91" s="25">
+        <v>583</v>
+      </c>
+      <c r="C91" s="25">
+        <v>2828</v>
+      </c>
+      <c r="D91" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="E91" s="25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="B92" s="25">
+        <v>1694</v>
+      </c>
+      <c r="C92" s="25">
+        <v>2316</v>
+      </c>
+      <c r="D92" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E92" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B93" s="25">
+        <v>1097</v>
+      </c>
+      <c r="C93" s="25">
+        <v>4011</v>
+      </c>
+      <c r="D93" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E93" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="B94" s="25">
+        <v>1070</v>
+      </c>
+      <c r="C94" s="25">
+        <v>3948</v>
+      </c>
+      <c r="D94" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="E94" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B95" s="25">
+        <v>1511</v>
+      </c>
+      <c r="C95" s="25">
+        <v>3967</v>
+      </c>
+      <c r="D95" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="E95" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="B96" s="25">
+        <v>614</v>
+      </c>
+      <c r="C96" s="25">
+        <v>2918</v>
+      </c>
+      <c r="D96" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E96" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B97" s="25">
+        <v>1386</v>
+      </c>
+      <c r="C97" s="25">
+        <v>4235</v>
+      </c>
+      <c r="D97" s="25" t="s">
+        <v>253</v>
+      </c>
+      <c r="E97" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B98" s="25">
+        <v>951</v>
+      </c>
+      <c r="C98" s="25">
+        <v>2742</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="E98" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B99" s="25">
+        <v>1361</v>
+      </c>
+      <c r="C99" s="25">
+        <v>3349</v>
+      </c>
+      <c r="D99" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="E99" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="B100" s="25">
+        <v>1823</v>
+      </c>
+      <c r="C100" s="25">
+        <v>3153</v>
+      </c>
+      <c r="D100" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="E100" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B101" s="25">
+        <v>1266</v>
+      </c>
+      <c r="C101" s="25">
+        <v>3404</v>
+      </c>
+      <c r="D101" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E101" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="B102" s="25">
+        <v>1485</v>
+      </c>
+      <c r="C102" s="25">
+        <v>3411</v>
+      </c>
+      <c r="D102" s="25" t="s">
+        <v>263</v>
+      </c>
+      <c r="E102" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="B103" s="25">
+        <v>1022</v>
+      </c>
+      <c r="C103" s="25">
+        <v>3532</v>
+      </c>
+      <c r="D103" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="E103" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="B104" s="25">
+        <v>983</v>
+      </c>
+      <c r="C104" s="25">
+        <v>3310</v>
+      </c>
+      <c r="D104" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="E104" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="B105" s="25">
+        <v>855</v>
+      </c>
+      <c r="C105" s="25">
+        <v>3223</v>
+      </c>
+      <c r="D105" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="E105" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="B106" s="25">
+        <v>1373</v>
+      </c>
+      <c r="C106" s="25">
+        <v>3371</v>
+      </c>
+      <c r="D106" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="E106" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="B107" s="25">
+        <v>1135</v>
+      </c>
+      <c r="C107" s="25">
+        <v>3750</v>
+      </c>
+      <c r="D107" s="25" t="s">
+        <v>273</v>
+      </c>
+      <c r="E107" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="B108" s="25">
+        <v>1194</v>
+      </c>
+      <c r="C108" s="25">
+        <v>3854</v>
+      </c>
+      <c r="D108" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="E108" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="B109" s="25">
+        <v>659</v>
+      </c>
+      <c r="C109" s="25">
+        <v>2926</v>
+      </c>
+      <c r="D109" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="E109" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="B110" s="25">
+        <v>1205</v>
+      </c>
+      <c r="C110" s="25">
+        <v>4064</v>
+      </c>
+      <c r="D110" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="E110" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B111" s="25">
+        <v>3215</v>
+      </c>
+      <c r="C111" s="25">
+        <v>3536</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="E111" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="B112" s="25">
+        <v>925</v>
+      </c>
+      <c r="C112" s="25">
+        <v>3971</v>
+      </c>
+      <c r="D112" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="E112" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="B113" s="25">
+        <v>2834</v>
+      </c>
+      <c r="C113" s="25">
+        <v>3046</v>
+      </c>
+      <c r="D113" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="E113" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="B114" s="25">
+        <v>1305</v>
+      </c>
+      <c r="C114" s="25">
+        <v>4187</v>
+      </c>
+      <c r="D114" s="25" t="s">
+        <v>287</v>
+      </c>
+      <c r="E114" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="B115" s="25">
+        <v>1200</v>
+      </c>
+      <c r="C115" s="25">
+        <v>4667</v>
+      </c>
+      <c r="D115" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="E115" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="B116" s="25">
+        <v>1251</v>
+      </c>
+      <c r="C116" s="25">
+        <v>4944</v>
+      </c>
+      <c r="D116" s="25" t="s">
+        <v>291</v>
+      </c>
+      <c r="E116" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="B117" s="25">
+        <v>1131</v>
+      </c>
+      <c r="C117" s="25">
+        <v>3915</v>
+      </c>
+      <c r="D117" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="E117" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B118" s="25">
+        <v>1234</v>
+      </c>
+      <c r="C118" s="25">
+        <v>4090</v>
+      </c>
+      <c r="D118" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="E118" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="B119" s="25">
+        <v>1181</v>
+      </c>
+      <c r="C119" s="25">
+        <v>3724</v>
+      </c>
+      <c r="D119" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="E119" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="B120" s="25">
+        <v>1099</v>
+      </c>
+      <c r="C120" s="25">
+        <v>4294</v>
+      </c>
+      <c r="D120" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E120" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="B121" s="25">
+        <v>1431</v>
+      </c>
+      <c r="C121" s="25">
+        <v>4305</v>
+      </c>
+      <c r="D121" s="25" t="s">
+        <v>301</v>
+      </c>
+      <c r="E121" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="B122" s="25">
+        <v>1407</v>
+      </c>
+      <c r="C122" s="25">
+        <v>5131</v>
+      </c>
+      <c r="D122" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="E122" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="B123" s="25">
+        <v>1258</v>
+      </c>
+      <c r="C123" s="25">
+        <v>4048</v>
+      </c>
+      <c r="D123" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E123" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="24" t="s">
+        <v>306</v>
+      </c>
+      <c r="B124" s="25">
+        <v>967</v>
+      </c>
+      <c r="C124" s="25">
+        <v>3838</v>
+      </c>
+      <c r="D124" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="E124" s="25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C168F5A-E815-0A44-A305-F0599336BDA7}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="27">
+        <v>1052.4780000000001</v>
+      </c>
+      <c r="D3" s="27">
+        <v>518.07669999999996</v>
+      </c>
+      <c r="E3" s="27">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="27">
+        <v>1093.7860000000001</v>
+      </c>
+      <c r="D4" s="27">
+        <v>446.44290000000001</v>
+      </c>
+      <c r="E4" s="27">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5" s="27">
+        <v>1041</v>
+      </c>
+      <c r="D5" s="27">
+        <v>353.4058</v>
+      </c>
+      <c r="E5" s="27">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="27">
+        <v>1466.6</v>
+      </c>
+      <c r="D6" s="27">
+        <v>825.73940000000005</v>
+      </c>
+      <c r="E6" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="27">
+        <v>1306.7270000000001</v>
+      </c>
+      <c r="D7" s="27">
+        <v>513.76260000000002</v>
+      </c>
+      <c r="E7" s="27">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="27">
+        <v>3280.6959999999999</v>
+      </c>
+      <c r="D8" s="27">
+        <v>647.16210000000001</v>
+      </c>
+      <c r="E8" s="27">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="27">
+        <v>3020.7139999999999</v>
+      </c>
+      <c r="D9" s="27">
+        <v>805.76409999999998</v>
+      </c>
+      <c r="E9" s="27">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="27">
+        <v>3266.8209999999999</v>
+      </c>
+      <c r="D10" s="27">
+        <v>756.78579999999999</v>
+      </c>
+      <c r="E10" s="27">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="27">
+        <v>3599.92</v>
+      </c>
+      <c r="D11" s="27">
+        <v>637.74940000000004</v>
+      </c>
+      <c r="E11" s="27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="27">
+        <v>3732.7269999999999</v>
+      </c>
+      <c r="D12" s="27">
+        <v>616.08860000000004</v>
+      </c>
+      <c r="E12" s="27">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9D46D0-A071-5E48-B8F9-D959A7777A3E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="25">
+        <v>0</v>
+      </c>
+      <c r="D2" s="25">
+        <v>-259.98136645962501</v>
+      </c>
+      <c r="E2" s="25">
+        <v>-901.27600866051102</v>
+      </c>
+      <c r="F2" s="25">
+        <v>381.31327574126101</v>
+      </c>
+      <c r="G2" s="25">
+        <v>0.79403741251873905</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="25">
+        <v>0</v>
+      </c>
+      <c r="D3" s="25">
+        <v>-13.8742236024832</v>
+      </c>
+      <c r="E3" s="25">
+        <v>-546.26048507432904</v>
+      </c>
+      <c r="F3" s="25">
+        <v>518.51203786936298</v>
+      </c>
+      <c r="G3" s="25">
+        <v>0.99999375551442504</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="25">
+        <v>0</v>
+      </c>
+      <c r="D4" s="25">
+        <v>319.22434782608798</v>
+      </c>
+      <c r="E4" s="25">
+        <v>-227.37786019118701</v>
+      </c>
+      <c r="F4" s="25">
+        <v>865.82655584336203</v>
+      </c>
+      <c r="G4" s="25">
+        <v>0.48900141972816602</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="25">
+        <v>0</v>
+      </c>
+      <c r="D5" s="25">
+        <v>452.03162055336003</v>
+      </c>
+      <c r="E5" s="25">
+        <v>-61.843759421820799</v>
+      </c>
+      <c r="F5" s="25">
+        <v>965.90700052854095</v>
+      </c>
+      <c r="G5" s="25">
+        <v>0.112752922698288</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="25">
+        <v>0</v>
+      </c>
+      <c r="D6" s="25">
+        <v>246.10714285714201</v>
+      </c>
+      <c r="E6" s="25">
+        <v>-373.14325894715398</v>
+      </c>
+      <c r="F6" s="25">
+        <v>865.35754466143703</v>
+      </c>
+      <c r="G6" s="25">
+        <v>0.80567717012331397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="25">
+        <v>0</v>
+      </c>
+      <c r="D7" s="25">
+        <v>579.20571428571304</v>
+      </c>
+      <c r="E7" s="25">
+        <v>-52.3082622343426</v>
+      </c>
+      <c r="F7" s="25">
+        <v>1210.7196908057699</v>
+      </c>
+      <c r="G7" s="25">
+        <v>8.8598116945589805E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="25">
+        <v>0</v>
+      </c>
+      <c r="D8" s="25">
+        <v>712.01298701298504</v>
+      </c>
+      <c r="E8" s="25">
+        <v>108.602815673912</v>
+      </c>
+      <c r="F8" s="25">
+        <v>1315.42315835206</v>
+      </c>
+      <c r="G8" s="25">
+        <v>1.2103948665193201E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="25">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25">
+        <v>333.09857142857101</v>
+      </c>
+      <c r="E9" s="25">
+        <v>-187.46479246537299</v>
+      </c>
+      <c r="F9" s="25">
+        <v>853.66193532251498</v>
+      </c>
+      <c r="G9" s="25">
+        <v>0.39433198785818002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="25">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25">
+        <v>465.905844155843</v>
+      </c>
+      <c r="E10" s="25">
+        <v>-20.180720319925101</v>
+      </c>
+      <c r="F10" s="25">
+        <v>951.99240863161106</v>
+      </c>
+      <c r="G10" s="25">
+        <v>6.7053436800587105E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="25">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25">
+        <v>132.80727272727199</v>
+      </c>
+      <c r="E11" s="25">
+        <v>-368.809105164485</v>
+      </c>
+      <c r="F11" s="25">
+        <v>634.42365061903001</v>
+      </c>
+      <c r="G11" s="25">
+        <v>0.94825310379988603</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
